--- a/Optimization Sheet.xlsx
+++ b/Optimization Sheet.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roney\Optimization-Course\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D738D4-7C2E-4DDA-972D-1FD2E7928DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A22867-EBF4-44F2-8999-FB94F98A9D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5AD50F6C-02AF-4DBD-AF8F-63AA420B5847}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="10000" windowHeight="11370" activeTab="1" xr2:uid="{5AD50F6C-02AF-4DBD-AF8F-63AA420B5847}"/>
   </bookViews>
   <sheets>
     <sheet name="ProjectSel1" sheetId="1" r:id="rId1"/>
-    <sheet name="Prosel" sheetId="2" r:id="rId2"/>
+    <sheet name="Prodline" sheetId="4" r:id="rId2"/>
+    <sheet name="Assemble" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,12 +38,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Profit</t>
   </si>
   <si>
     <t>Max</t>
+  </si>
+  <si>
+    <t>Type1</t>
+  </si>
+  <si>
+    <t>Type2</t>
+  </si>
+  <si>
+    <t>Type3</t>
+  </si>
+  <si>
+    <t>Type4</t>
+  </si>
+  <si>
+    <t>Type5</t>
+  </si>
+  <si>
+    <t>Mach 1</t>
+  </si>
+  <si>
+    <t>Mach 2</t>
+  </si>
+  <si>
+    <t>Mach 3</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>m1</t>
+  </si>
+  <si>
+    <t>m2</t>
+  </si>
+  <si>
+    <t>Cases</t>
+  </si>
+  <si>
+    <t>chemicals</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>Cost</t>
   </si>
 </sst>
 </file>
@@ -951,10 +1000,204 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C0C024A-B567-40BB-8B82-3F60452BAEFF}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD106F12-F98F-46B2-AF8E-5AAD2FC48A9D}">
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>1.6</v>
+      </c>
+      <c r="C4">
+        <v>1.25</v>
+      </c>
+      <c r="D4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>125</v>
+      </c>
+      <c r="C6">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>375</v>
+      </c>
+      <c r="C7">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>1.875</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A3BD829-11CA-4D4E-AA3B-AE70ED39CE68}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B2">
+        <v>18500</v>
+      </c>
+      <c r="C2">
+        <v>25000</v>
+      </c>
+      <c r="D2">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>265</v>
+      </c>
+      <c r="D4">
+        <v>200</v>
+      </c>
+      <c r="E4">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>130</v>
+      </c>
+      <c r="C5">
+        <v>235</v>
+      </c>
+      <c r="D5">
+        <v>160</v>
+      </c>
+      <c r="E5">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>140</v>
+      </c>
+      <c r="C6">
+        <v>170</v>
+      </c>
+      <c r="D6">
+        <v>260</v>
+      </c>
+      <c r="E6">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>210</v>
+      </c>
+      <c r="C7">
+        <v>220</v>
+      </c>
+      <c r="D7">
+        <v>180</v>
+      </c>
+      <c r="E7">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>80</v>
+      </c>
+      <c r="C8">
+        <v>120</v>
+      </c>
+      <c r="D8">
+        <v>220</v>
+      </c>
+      <c r="E8">
+        <v>2500</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Optimization Sheet.xlsx
+++ b/Optimization Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roney\Optimization-Course\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A22867-EBF4-44F2-8999-FB94F98A9D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8DF108-F8CA-4D19-AD64-692B982570E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="10000" windowHeight="11370" activeTab="1" xr2:uid="{5AD50F6C-02AF-4DBD-AF8F-63AA420B5847}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="10000" windowHeight="11370" firstSheet="1" activeTab="2" xr2:uid="{5AD50F6C-02AF-4DBD-AF8F-63AA420B5847}"/>
   </bookViews>
   <sheets>
     <sheet name="ProjectSel1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>Profit</t>
   </si>
@@ -1095,8 +1095,14 @@
       <c r="D1" t="s">
         <v>9</v>
       </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
       <c r="B2">
         <v>18500</v>
       </c>
@@ -1105,11 +1111,6 @@
       </c>
       <c r="D2">
         <v>35000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="E3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">

--- a/Optimization Sheet.xlsx
+++ b/Optimization Sheet.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roney\Optimization-Course\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8DF108-F8CA-4D19-AD64-692B982570E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8275D2C5-6E99-4996-B712-49F68A12E702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="10000" windowHeight="11370" firstSheet="1" activeTab="2" xr2:uid="{5AD50F6C-02AF-4DBD-AF8F-63AA420B5847}"/>
+    <workbookView xWindow="9770" yWindow="110" windowWidth="10000" windowHeight="10850" firstSheet="3" activeTab="3" xr2:uid="{5AD50F6C-02AF-4DBD-AF8F-63AA420B5847}"/>
   </bookViews>
   <sheets>
     <sheet name="ProjectSel1" sheetId="1" r:id="rId1"/>
     <sheet name="Prodline" sheetId="4" r:id="rId2"/>
     <sheet name="Assemble" sheetId="3" r:id="rId3"/>
+    <sheet name="MandD" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>Profit</t>
   </si>
@@ -92,13 +93,55 @@
   </si>
   <si>
     <t>Cost</t>
+  </si>
+  <si>
+    <t>Tacoma</t>
+  </si>
+  <si>
+    <t>San Diego</t>
+  </si>
+  <si>
+    <t>Dallas</t>
+  </si>
+  <si>
+    <t>Denver</t>
+  </si>
+  <si>
+    <t>St. Louis</t>
+  </si>
+  <si>
+    <t>Tampa</t>
+  </si>
+  <si>
+    <t>Baltimore</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Macon</t>
+  </si>
+  <si>
+    <t>Louisville</t>
+  </si>
+  <si>
+    <t>Detroit</t>
+  </si>
+  <si>
+    <t>Phoenix</t>
+  </si>
+  <si>
+    <t>Dmin</t>
+  </si>
+  <si>
+    <t>Dmax</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,6 +153,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF030712"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -133,13 +182,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1201,4 +1253,233 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{160F7415-4A1A-4BF6-B513-6A60DEA84C0F}">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="C2" s="3">
+        <v>2.75</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="E2" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="H2" s="3">
+        <v>1.65</v>
+      </c>
+      <c r="I2" s="3">
+        <v>18000</v>
+      </c>
+      <c r="J2" s="3">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1.85</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1.85</v>
+      </c>
+      <c r="I3" s="3">
+        <v>15000</v>
+      </c>
+      <c r="J3" s="3">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2.25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1.85</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="G4" s="3">
+        <v>2.25</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2</v>
+      </c>
+      <c r="I4" s="3">
+        <v>25000</v>
+      </c>
+      <c r="J4" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="H5" s="3">
+        <v>2.65</v>
+      </c>
+      <c r="I5" s="3">
+        <v>20000</v>
+      </c>
+      <c r="J5" s="3">
+        <v>36.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="3">
+        <f>8500*0.8</f>
+        <v>6800</v>
+      </c>
+      <c r="C6" s="3">
+        <f>0.8*14500</f>
+        <v>11600</v>
+      </c>
+      <c r="D6" s="3">
+        <f>0.8*13500</f>
+        <v>10800</v>
+      </c>
+      <c r="E6" s="3">
+        <f>0.8*12600</f>
+        <v>10080</v>
+      </c>
+      <c r="F6" s="3">
+        <f>0.8*18000</f>
+        <v>14400</v>
+      </c>
+      <c r="G6" s="3">
+        <f>0.8*15000</f>
+        <v>12000</v>
+      </c>
+      <c r="H6" s="3">
+        <f>0.8*9000</f>
+        <v>7200</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="2">
+        <v>8500</v>
+      </c>
+      <c r="C7" s="2">
+        <v>14500</v>
+      </c>
+      <c r="D7" s="2">
+        <v>13500</v>
+      </c>
+      <c r="E7" s="2">
+        <v>12600</v>
+      </c>
+      <c r="F7" s="2">
+        <v>18000</v>
+      </c>
+      <c r="G7" s="2">
+        <v>15000</v>
+      </c>
+      <c r="H7" s="2">
+        <v>9000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Optimization Sheet.xlsx
+++ b/Optimization Sheet.xlsx
@@ -1,23 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roney\Optimization-Course\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8275D2C5-6E99-4996-B712-49F68A12E702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B39F2A-10CB-4F1C-A5C9-EF1F38A39CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9770" yWindow="110" windowWidth="10000" windowHeight="10850" firstSheet="3" activeTab="3" xr2:uid="{5AD50F6C-02AF-4DBD-AF8F-63AA420B5847}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="5" xr2:uid="{5AD50F6C-02AF-4DBD-AF8F-63AA420B5847}"/>
   </bookViews>
   <sheets>
     <sheet name="ProjectSel1" sheetId="1" r:id="rId1"/>
     <sheet name="Prodline" sheetId="4" r:id="rId2"/>
     <sheet name="Assemble" sheetId="3" r:id="rId3"/>
     <sheet name="MandD" sheetId="5" r:id="rId4"/>
+    <sheet name="Rocks" sheetId="7" r:id="rId5"/>
+    <sheet name="Hosp" sheetId="8" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="3" hidden="1">0</definedName>
+    <definedName name="solver_opt" localSheetId="3" hidden="1">MandD!$G$13</definedName>
+    <definedName name="solver_typ" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
   <si>
     <t>Profit</t>
   </si>
@@ -135,6 +146,42 @@
   </si>
   <si>
     <t>Dmax</t>
+  </si>
+  <si>
+    <t>Fine</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Coarse</t>
+  </si>
+  <si>
+    <t>Limestone</t>
+  </si>
+  <si>
+    <t>Chat</t>
+  </si>
+  <si>
+    <t>Redi-Mix</t>
+  </si>
+  <si>
+    <t>Rough</t>
+  </si>
+  <si>
+    <t>Stay (hours)</t>
+  </si>
+  <si>
+    <t>Surg</t>
+  </si>
+  <si>
+    <t>Face</t>
+  </si>
+  <si>
+    <t>Lipo</t>
+  </si>
+  <si>
+    <t>Implant</t>
   </si>
 </sst>
 </file>
@@ -190,7 +237,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1482,4 +1529,186 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7FCDFE3-0DDB-4D3F-BB29-2883F62540C3}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3">
+        <v>0.5</v>
+      </c>
+      <c r="C3">
+        <v>0.2</v>
+      </c>
+      <c r="D3">
+        <v>0.05</v>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4">
+        <v>0.3</v>
+      </c>
+      <c r="C4">
+        <v>0.4</v>
+      </c>
+      <c r="D4">
+        <v>0.2</v>
+      </c>
+      <c r="E4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5">
+        <v>0.2</v>
+      </c>
+      <c r="C5">
+        <v>0.3</v>
+      </c>
+      <c r="D5">
+        <v>0.35</v>
+      </c>
+      <c r="E5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0.1</v>
+      </c>
+      <c r="D6">
+        <v>0.4</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E766485-B35E-475A-B21A-7CB0AA5A0953}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>240</v>
+      </c>
+      <c r="C2">
+        <v>225</v>
+      </c>
+      <c r="D2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3">
+        <f>3*24</f>
+        <v>72</v>
+      </c>
+      <c r="C3">
+        <f>5*24</f>
+        <v>120</v>
+      </c>
+      <c r="D3">
+        <f>6*24</f>
+        <v>144</v>
+      </c>
+      <c r="E3">
+        <f>70*7*24</f>
+        <v>11760</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1.5</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>165</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Optimization Sheet.xlsx
+++ b/Optimization Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roney\Optimization-Course\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCF56BF-5F42-4164-8330-D800E9DE53D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74949F8B-8DCB-4E24-8374-9847B90909CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="8170" firstSheet="3" activeTab="6" xr2:uid="{5AD50F6C-02AF-4DBD-AF8F-63AA420B5847}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="7" activeTab="8" xr2:uid="{5AD50F6C-02AF-4DBD-AF8F-63AA420B5847}"/>
   </bookViews>
   <sheets>
     <sheet name="ProjectSel1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="Rocks" sheetId="7" r:id="rId5"/>
     <sheet name="Hosp" sheetId="8" r:id="rId6"/>
     <sheet name="Butter" sheetId="10" r:id="rId7"/>
+    <sheet name="PetFood" sheetId="11" r:id="rId8"/>
+    <sheet name="Sced" sheetId="12" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
@@ -51,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="74">
   <si>
     <t>Profit</t>
   </si>
@@ -183,6 +185,96 @@
   </si>
   <si>
     <t>Implant</t>
+  </si>
+  <si>
+    <t>Peanut Butter</t>
+  </si>
+  <si>
+    <t>Apple Butter</t>
+  </si>
+  <si>
+    <t>Packaging (hours)</t>
+  </si>
+  <si>
+    <t>Sterilizer</t>
+  </si>
+  <si>
+    <t>Packaging</t>
+  </si>
+  <si>
+    <t>Bird Food</t>
+  </si>
+  <si>
+    <t>Dog Food</t>
+  </si>
+  <si>
+    <t>Blending (hours)</t>
+  </si>
+  <si>
+    <t>Seeds</t>
+  </si>
+  <si>
+    <t>Stones</t>
+  </si>
+  <si>
+    <t>Cereal</t>
+  </si>
+  <si>
+    <t>Meat</t>
+  </si>
+  <si>
+    <t>Fishmeal</t>
+  </si>
+  <si>
+    <t>Protein %</t>
+  </si>
+  <si>
+    <t>Carbs %</t>
+  </si>
+  <si>
+    <t>Trace Min %</t>
+  </si>
+  <si>
+    <t>Abrasives %</t>
+  </si>
+  <si>
+    <t>Cost $/ton</t>
+  </si>
+  <si>
+    <t>Min Protein %</t>
+  </si>
+  <si>
+    <t>Min Carbs %</t>
+  </si>
+  <si>
+    <t>Min Trace Min %</t>
+  </si>
+  <si>
+    <t>Min Abrasives %</t>
+  </si>
+  <si>
+    <t>Min Seeds %</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
   </si>
 </sst>
 </file>
@@ -230,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -241,6 +333,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1716,9 +1812,442 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5569F7CD-0F93-45E4-AC41-3B9629D5D7F8}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1100</v>
+      </c>
+      <c r="C2">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83F959D2-A202-44B3-841F-A00500C7E3D7}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5">
+        <v>750</v>
+      </c>
+      <c r="C2" s="5">
+        <v>980</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="D3" s="5">
+        <v>8</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="D4" s="5">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="5">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5">
+        <v>12</v>
+      </c>
+      <c r="F7" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="5">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>30</v>
+      </c>
+      <c r="E8" s="5">
+        <v>10</v>
+      </c>
+      <c r="F8" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="5">
+        <v>2</v>
+      </c>
+      <c r="C9" s="5">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5">
+        <v>100</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="5">
+        <v>700</v>
+      </c>
+      <c r="C11" s="5">
+        <v>100</v>
+      </c>
+      <c r="D11" s="5">
+        <v>200</v>
+      </c>
+      <c r="E11" s="5">
+        <v>600</v>
+      </c>
+      <c r="F11" s="5">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="5">
+        <v>5</v>
+      </c>
+      <c r="C14" s="5">
+        <v>11</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="5">
+        <v>18</v>
+      </c>
+      <c r="C15" s="5">
+        <v>15</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="5">
+        <v>2</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="5">
+        <v>10</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01584D7C-35B9-4302-B914-56B7552FDFA7}">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B1" s="5">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="5">
+        <v>680</v>
+      </c>
+      <c r="C2" s="5">
+        <v>705</v>
+      </c>
+      <c r="D2" s="5">
+        <v>705</v>
+      </c>
+      <c r="E2" s="5">
+        <v>705</v>
+      </c>
+      <c r="F2" s="5">
+        <v>705</v>
+      </c>
+      <c r="G2" s="5">
+        <v>680</v>
+      </c>
+      <c r="H2" s="5">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="5">
+        <v>17302.201179395699</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="5">
+        <v>25631.13259405359</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="5">
+        <v>21101.467706169988</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" s="5">
+        <v>24919.494948545263</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" s="5">
+        <v>23554.342347762002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="5">
+        <v>20388.683176086881</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="5">
+        <v>17707.072962883474</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Optimization Sheet.xlsx
+++ b/Optimization Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roney\Optimization-Course\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74949F8B-8DCB-4E24-8374-9847B90909CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2E11B2-EAD1-4957-AB99-69FF5446AE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="7" activeTab="8" xr2:uid="{5AD50F6C-02AF-4DBD-AF8F-63AA420B5847}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7" activeTab="11" xr2:uid="{5AD50F6C-02AF-4DBD-AF8F-63AA420B5847}"/>
   </bookViews>
   <sheets>
     <sheet name="ProjectSel1" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,9 @@
     <sheet name="Butter" sheetId="10" r:id="rId7"/>
     <sheet name="PetFood" sheetId="11" r:id="rId8"/>
     <sheet name="Sced" sheetId="12" r:id="rId9"/>
+    <sheet name="Lockbox" sheetId="13" r:id="rId10"/>
+    <sheet name="Farming" sheetId="14" r:id="rId11"/>
+    <sheet name="Inv" sheetId="15" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
@@ -53,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="110">
   <si>
     <t>Profit</t>
   </si>
@@ -275,6 +278,114 @@
   </si>
   <si>
     <t>Saturday</t>
+  </si>
+  <si>
+    <t>Sacramento</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York </t>
+  </si>
+  <si>
+    <t>Atlanta</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>Mid-Atlantic</t>
+  </si>
+  <si>
+    <t>Midwest</t>
+  </si>
+  <si>
+    <t>Northeast</t>
+  </si>
+  <si>
+    <t>Northwest</t>
+  </si>
+  <si>
+    <t>Southeast</t>
+  </si>
+  <si>
+    <t>Southwest</t>
+  </si>
+  <si>
+    <t>Milo</t>
+  </si>
+  <si>
+    <t>Cotton</t>
+  </si>
+  <si>
+    <t>Wheat</t>
+  </si>
+  <si>
+    <t>Farm 1 Acres</t>
+  </si>
+  <si>
+    <t>Farm 1 Water</t>
+  </si>
+  <si>
+    <t>Farm 2 Acres</t>
+  </si>
+  <si>
+    <t>Farm 2 Water</t>
+  </si>
+  <si>
+    <t>Farm 3 Acres</t>
+  </si>
+  <si>
+    <t>Farm 3 Water</t>
+  </si>
+  <si>
+    <t>Harvest Cap</t>
+  </si>
+  <si>
+    <t>Demand - Lights</t>
+  </si>
+  <si>
+    <t>Demand - Heavies</t>
+  </si>
+  <si>
+    <t>Fixed Cost - Light</t>
+  </si>
+  <si>
+    <t>Fixed Cost - Heavy</t>
+  </si>
+  <si>
+    <t>Var Cost - Light (owned)</t>
+  </si>
+  <si>
+    <t>Var Cost - Heavy (owned)</t>
+  </si>
+  <si>
+    <t>Var Cost - Light (rent)</t>
+  </si>
+  <si>
+    <t>Var Cost - Heavy (rent)</t>
+  </si>
+  <si>
+    <t>Day 1</t>
+  </si>
+  <si>
+    <t>Day 2</t>
+  </si>
+  <si>
+    <t>Day 3</t>
+  </si>
+  <si>
+    <t>Day 4</t>
+  </si>
+  <si>
+    <t>Day 5</t>
+  </si>
+  <si>
+    <t>Day 6</t>
+  </si>
+  <si>
+    <t>Day 7</t>
   </si>
 </sst>
 </file>
@@ -322,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -336,6 +447,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1195,6 +1311,561 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{427C3170-A3CB-4F7D-BE35-967AAD1607EA}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="1">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1">
+        <v>13.5</v>
+      </c>
+      <c r="D2" s="1">
+        <v>13.5</v>
+      </c>
+      <c r="E2" s="1">
+        <v>13.5</v>
+      </c>
+      <c r="F2" s="1">
+        <v>20.25</v>
+      </c>
+      <c r="G2" s="1">
+        <v>20.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="1">
+        <v>58.5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>39</v>
+      </c>
+      <c r="D3" s="1">
+        <v>29.25</v>
+      </c>
+      <c r="E3" s="1">
+        <v>39</v>
+      </c>
+      <c r="F3" s="1">
+        <v>19.5</v>
+      </c>
+      <c r="G3" s="1">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="E4" s="1">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="G4" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="1">
+        <v>81</v>
+      </c>
+      <c r="C5" s="1">
+        <v>54</v>
+      </c>
+      <c r="D5" s="1">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1">
+        <v>67.5</v>
+      </c>
+      <c r="F5" s="1">
+        <v>27</v>
+      </c>
+      <c r="G5" s="1">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="1">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="D6" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>42</v>
+      </c>
+      <c r="F6" s="1">
+        <v>63</v>
+      </c>
+      <c r="G6" s="1">
+        <v>73.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="1">
+        <v>84</v>
+      </c>
+      <c r="C7" s="1">
+        <v>48</v>
+      </c>
+      <c r="D7" s="1">
+        <v>36</v>
+      </c>
+      <c r="E7" s="1">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1">
+        <v>48</v>
+      </c>
+      <c r="G7" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="1">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1">
+        <v>27</v>
+      </c>
+      <c r="D8" s="1">
+        <v>54</v>
+      </c>
+      <c r="E8" s="1">
+        <v>18</v>
+      </c>
+      <c r="F8" s="1">
+        <v>63</v>
+      </c>
+      <c r="G8" s="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1">
+        <v>60</v>
+      </c>
+      <c r="D9" s="1">
+        <v>35</v>
+      </c>
+      <c r="E9" s="1">
+        <v>35</v>
+      </c>
+      <c r="F9" s="1">
+        <v>30</v>
+      </c>
+      <c r="G9" s="1">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FD88E8-0A3C-4754-954C-D66EA8D04C4B}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="6">
+        <v>400</v>
+      </c>
+      <c r="C2" s="6">
+        <v>300</v>
+      </c>
+      <c r="D2" s="6">
+        <v>100</v>
+      </c>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="6">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="6">
+        <v>6</v>
+      </c>
+      <c r="C4" s="6">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6">
+        <v>2</v>
+      </c>
+      <c r="E4" s="6">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="6">
+        <v>6</v>
+      </c>
+      <c r="C6" s="6">
+        <v>4</v>
+      </c>
+      <c r="D6" s="6">
+        <v>2</v>
+      </c>
+      <c r="E6" s="6">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="6">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="6">
+        <v>6</v>
+      </c>
+      <c r="C8" s="6">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6">
+        <v>2</v>
+      </c>
+      <c r="E8" s="6">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="6">
+        <v>700</v>
+      </c>
+      <c r="C9" s="6">
+        <v>800</v>
+      </c>
+      <c r="D9" s="6">
+        <v>300</v>
+      </c>
+      <c r="E9" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4596B163-DAD2-4035-9751-BF03E630A3C8}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="8"/>
+      <c r="B1" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="8">
+        <v>6</v>
+      </c>
+      <c r="C2" s="8">
+        <v>3</v>
+      </c>
+      <c r="D2" s="8">
+        <v>5</v>
+      </c>
+      <c r="E2" s="8">
+        <v>8</v>
+      </c>
+      <c r="F2" s="8">
+        <v>2</v>
+      </c>
+      <c r="G2" s="8">
+        <v>4</v>
+      </c>
+      <c r="H2" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0</v>
+      </c>
+      <c r="C3" s="8">
+        <v>2</v>
+      </c>
+      <c r="D3" s="8">
+        <v>4</v>
+      </c>
+      <c r="E3" s="8">
+        <v>3</v>
+      </c>
+      <c r="F3" s="8">
+        <v>1</v>
+      </c>
+      <c r="G3" s="8">
+        <v>4</v>
+      </c>
+      <c r="H3" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="8">
+        <v>32</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="8">
+        <v>44</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="8">
+        <v>40</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="8">
+        <v>54</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="8">
+        <v>175</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="8">
+        <v>225</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD106F12-F98F-46B2-AF8E-5AAD2FC48A9D}">
   <dimension ref="A1:D9"/>
@@ -1876,256 +2547,232 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="5"/>
-      <c r="B1" s="5" t="s">
+      <c r="B1" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2">
         <v>750</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2">
         <v>980</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3">
         <v>0.25</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3">
         <v>0.15</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3">
         <v>8</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>0.1</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4">
         <v>0.3</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4">
         <v>8</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
+      <c r="A7" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>10</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7">
         <v>0</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7">
         <v>3</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7">
         <v>12</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+      <c r="A8" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8">
         <v>10</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8">
         <v>0</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8">
         <v>30</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8">
         <v>10</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+      <c r="A9" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9">
         <v>3</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9">
         <v>0</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+      <c r="A10" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10">
         <v>100</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10">
         <v>0</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="5" t="s">
+      <c r="A11" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11">
         <v>700</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11">
         <v>100</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11">
         <v>200</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11">
         <v>600</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11">
         <v>900</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5" t="s">
+      <c r="B13" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
+      <c r="A14" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14">
         <v>5</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14">
         <v>11</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="5" t="s">
+      <c r="A15" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15">
         <v>18</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15">
         <v>15</v>
       </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
+      <c r="A16" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16">
         <v>1</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="5" t="s">
+      <c r="A17" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17">
         <v>2</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
+      <c r="A18" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18">
         <v>0</v>
       </c>
     </row>
@@ -2140,25 +2787,25 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B1" s="5">
+      <c r="B1">
         <v>1</v>
       </c>
-      <c r="C1" s="5">
+      <c r="C1">
         <v>2</v>
       </c>
-      <c r="D1" s="5">
+      <c r="D1">
         <v>3</v>
       </c>
-      <c r="E1" s="5">
+      <c r="E1">
         <v>4</v>
       </c>
-      <c r="F1" s="5">
+      <c r="F1">
         <v>5</v>
       </c>
-      <c r="G1" s="5">
+      <c r="G1">
         <v>6</v>
       </c>
-      <c r="H1" s="5">
+      <c r="H1">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -2169,25 +2816,25 @@
       <c r="A2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2">
         <v>680</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2">
         <v>705</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2">
         <v>705</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2">
         <v>705</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2">
         <v>705</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2">
         <v>680</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2">
         <v>655</v>
       </c>
     </row>
@@ -2195,7 +2842,7 @@
       <c r="A3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3">
         <v>17302.201179395699</v>
       </c>
     </row>
@@ -2203,7 +2850,7 @@
       <c r="A4" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4">
         <v>25631.13259405359</v>
       </c>
     </row>
@@ -2211,7 +2858,7 @@
       <c r="A5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5">
         <v>21101.467706169988</v>
       </c>
     </row>
@@ -2219,7 +2866,7 @@
       <c r="A6" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6">
         <v>24919.494948545263</v>
       </c>
     </row>
@@ -2227,7 +2874,7 @@
       <c r="A7" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7">
         <v>23554.342347762002</v>
       </c>
     </row>
@@ -2235,7 +2882,7 @@
       <c r="A8" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8">
         <v>20388.683176086881</v>
       </c>
     </row>
@@ -2243,7 +2890,7 @@
       <c r="A9" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9">
         <v>17707.072962883474</v>
       </c>
     </row>

--- a/Optimization Sheet.xlsx
+++ b/Optimization Sheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roney\Optimization-Course\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2E11B2-EAD1-4957-AB99-69FF5446AE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB155CB-D634-409E-8BF0-E811924A648F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="7" activeTab="11" xr2:uid="{5AD50F6C-02AF-4DBD-AF8F-63AA420B5847}"/>
+    <workbookView xWindow="1780" yWindow="1780" windowWidth="14400" windowHeight="8170" firstSheet="13" activeTab="18" xr2:uid="{5AD50F6C-02AF-4DBD-AF8F-63AA420B5847}"/>
   </bookViews>
   <sheets>
     <sheet name="ProjectSel1" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,13 @@
     <sheet name="Lockbox" sheetId="13" r:id="rId10"/>
     <sheet name="Farming" sheetId="14" r:id="rId11"/>
     <sheet name="Inv" sheetId="15" r:id="rId12"/>
+    <sheet name="InvDep" sheetId="16" r:id="rId13"/>
+    <sheet name="Phone" sheetId="17" r:id="rId14"/>
+    <sheet name="Nuts" sheetId="18" r:id="rId15"/>
+    <sheet name="Snow" sheetId="19" r:id="rId16"/>
+    <sheet name="Snow1" sheetId="20" r:id="rId17"/>
+    <sheet name="Net" sheetId="21" r:id="rId18"/>
+    <sheet name="Net1" sheetId="22" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
@@ -56,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="151">
   <si>
     <t>Profit</t>
   </si>
@@ -386,13 +393,136 @@
   </si>
   <si>
     <t>Day 7</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>Exp</t>
+  </si>
+  <si>
+    <t>Rev</t>
+  </si>
+  <si>
+    <t>Fruit</t>
+  </si>
+  <si>
+    <t>Veggie</t>
+  </si>
+  <si>
+    <t>Hour</t>
+  </si>
+  <si>
+    <t>Eng Demand</t>
+  </si>
+  <si>
+    <t>Span Demand</t>
+  </si>
+  <si>
+    <t>Chalet</t>
+  </si>
+  <si>
+    <t>Hovel</t>
+  </si>
+  <si>
+    <t>Peanuts</t>
+  </si>
+  <si>
+    <t>Walnuts</t>
+  </si>
+  <si>
+    <t>Almonds</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Month 1 - Nut Prices</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Availability</t>
+  </si>
+  <si>
+    <t>Month 2 - Nut Prices</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Month 1 Price</t>
+  </si>
+  <si>
+    <t>Month 2 Price</t>
+  </si>
+  <si>
+    <t>Max Peanuts %</t>
+  </si>
+  <si>
+    <t>Min Almonds %</t>
+  </si>
+  <si>
+    <t>Max production/month</t>
+  </si>
+  <si>
+    <t>Storage cost/lb/month</t>
+  </si>
+  <si>
+    <t>Min Chalet Month 2</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Katy</t>
+  </si>
+  <si>
+    <t>Wharton</t>
+  </si>
+  <si>
+    <t>Kiowa</t>
+  </si>
+  <si>
+    <t>Waha</t>
+  </si>
+  <si>
+    <t>Carthage</t>
+  </si>
+  <si>
+    <t>Joliet</t>
+  </si>
+  <si>
+    <t>Henry</t>
+  </si>
+  <si>
+    <t>Perrville</t>
+  </si>
+  <si>
+    <t>Lebanon</t>
+  </si>
+  <si>
+    <t>Maumee</t>
+  </si>
+  <si>
+    <t>Leidy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -411,6 +541,12 @@
       <color rgb="FF030712"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -433,7 +569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -450,9 +586,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1532,151 +1666,148 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6" t="s">
+      <c r="B1" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
         <v>400</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2">
         <v>300</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+      <c r="A3" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3">
         <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="A4" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4">
         <v>6</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4">
         <v>4</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4">
         <v>2</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4">
         <v>1500</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5">
         <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6">
         <v>6</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6">
         <v>4</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6">
         <v>2</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6">
         <v>2000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7">
         <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+      <c r="A8" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8">
         <v>6</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8">
         <v>4</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8">
         <v>2</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8">
         <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" t="s">
+      <c r="A9" t="s">
         <v>94</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9">
         <v>700</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9">
         <v>800</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9">
         <v>300</v>
       </c>
-      <c r="E9" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1692,174 +1823,1953 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="8"/>
-      <c r="B1" s="8" t="s">
+      <c r="B1" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2">
         <v>6</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2">
         <v>3</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2">
         <v>5</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2">
         <v>8</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2">
         <v>2</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2">
         <v>4</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="8">
-        <v>0</v>
-      </c>
-      <c r="C3" s="8">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3">
         <v>4</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3">
         <v>3</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3">
         <v>4</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-    </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+      <c r="A5" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5">
         <v>32</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6">
         <v>44</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
+      <c r="A7" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7">
         <v>40</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+      <c r="A8" t="s">
         <v>100</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8">
         <v>54</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9">
         <v>175</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10">
         <v>225</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D2F5A2-C5EB-413A-AE54-767837BE96F0}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2">
+        <v>3.8</v>
+      </c>
+      <c r="C2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>1.5</v>
+      </c>
+      <c r="C3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>18</v>
+      </c>
+      <c r="D5">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>12000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E2B3FF6-D15E-42FB-AEE2-1BA8AB47EAFB}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+      <c r="N1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>6</v>
+      </c>
+      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+      <c r="N2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+      <c r="N3">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8AF5491-8908-4A2D-83AB-CBDD0FEDA6CF}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2">
+        <v>0.2</v>
+      </c>
+      <c r="C2">
+        <v>0.35</v>
+      </c>
+      <c r="D2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3">
+        <v>400</v>
+      </c>
+      <c r="C3">
+        <v>999999</v>
+      </c>
+      <c r="D3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6">
+        <v>0.19</v>
+      </c>
+      <c r="C6">
+        <v>0.36</v>
+      </c>
+      <c r="D6">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7">
+        <v>500</v>
+      </c>
+      <c r="C7">
+        <v>999999</v>
+      </c>
+      <c r="D7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10">
+        <v>0.8</v>
+      </c>
+      <c r="C10">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11">
+        <v>0.81</v>
+      </c>
+      <c r="C11">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12">
+        <v>0.25</v>
+      </c>
+      <c r="C12">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13">
+        <v>0.4</v>
+      </c>
+      <c r="C13">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B17">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16E4AEA4-4A09-43F1-B827-C942EE841FD5}">
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>52020.000000000007</v>
+      </c>
+      <c r="C2">
+        <v>21419.999999999996</v>
+      </c>
+      <c r="D2">
+        <v>74970.000000000015</v>
+      </c>
+      <c r="E2">
+        <v>113220.00000000001</v>
+      </c>
+      <c r="F2">
+        <v>142290.00000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>36480</v>
+      </c>
+      <c r="C3">
+        <v>31920</v>
+      </c>
+      <c r="D3">
+        <v>126160.00000000001</v>
+      </c>
+      <c r="E3">
+        <v>138320</v>
+      </c>
+      <c r="F3">
+        <v>133760.00000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>21560</v>
+      </c>
+      <c r="C4">
+        <v>44660</v>
+      </c>
+      <c r="D4">
+        <v>56980.000000000015</v>
+      </c>
+      <c r="E4">
+        <v>144760.00000000003</v>
+      </c>
+      <c r="F4">
+        <v>132440</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>35880</v>
+      </c>
+      <c r="C5">
+        <v>49680.000000000007</v>
+      </c>
+      <c r="D5">
+        <v>62100</v>
+      </c>
+      <c r="E5">
+        <v>113160</v>
+      </c>
+      <c r="F5">
+        <v>122820.00000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>19050.000000000004</v>
+      </c>
+      <c r="C6">
+        <v>39370.000000000007</v>
+      </c>
+      <c r="D6">
+        <v>26670</v>
+      </c>
+      <c r="E6">
+        <v>100330</v>
+      </c>
+      <c r="F6">
+        <v>111760.00000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>54180.000000000007</v>
+      </c>
+      <c r="C7">
+        <v>63210.000000000007</v>
+      </c>
+      <c r="D7">
+        <v>83850.000000000015</v>
+      </c>
+      <c r="E7">
+        <v>99330</v>
+      </c>
+      <c r="F7">
+        <v>78690</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>53280</v>
+      </c>
+      <c r="C8">
+        <v>68820.000000000015</v>
+      </c>
+      <c r="D8">
+        <v>109890.00000000001</v>
+      </c>
+      <c r="E8">
+        <v>68820.000000000015</v>
+      </c>
+      <c r="F8">
+        <v>63270.000000000007</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>59400.000000000007</v>
+      </c>
+      <c r="C9">
+        <v>66000.000000000015</v>
+      </c>
+      <c r="D9">
+        <v>57200</v>
+      </c>
+      <c r="E9">
+        <v>83600</v>
+      </c>
+      <c r="F9">
+        <v>53900.000000000007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>40300.000000000007</v>
+      </c>
+      <c r="C10">
+        <v>53300</v>
+      </c>
+      <c r="D10">
+        <v>85800</v>
+      </c>
+      <c r="E10">
+        <v>97500</v>
+      </c>
+      <c r="F10">
+        <v>93600.000000000015</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>43200.000000000007</v>
+      </c>
+      <c r="C11">
+        <v>87750</v>
+      </c>
+      <c r="D11">
+        <v>95850</v>
+      </c>
+      <c r="E11">
+        <v>81000.000000000015</v>
+      </c>
+      <c r="F11">
+        <v>112050.00000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="1"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1DD8ED-F2F6-4F44-9A08-A5B108D3BD5A}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>153</v>
+      </c>
+      <c r="C2" s="2">
+        <v>153</v>
+      </c>
+      <c r="D2" s="2">
+        <v>153</v>
+      </c>
+      <c r="E2" s="2">
+        <v>153</v>
+      </c>
+      <c r="F2" s="2">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>152</v>
+      </c>
+      <c r="C3">
+        <v>152</v>
+      </c>
+      <c r="D3">
+        <v>152</v>
+      </c>
+      <c r="E3">
+        <v>152</v>
+      </c>
+      <c r="F3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>154</v>
+      </c>
+      <c r="C4">
+        <v>154</v>
+      </c>
+      <c r="D4">
+        <v>154</v>
+      </c>
+      <c r="E4">
+        <v>154</v>
+      </c>
+      <c r="F4">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>138</v>
+      </c>
+      <c r="C5">
+        <v>138</v>
+      </c>
+      <c r="D5">
+        <v>138</v>
+      </c>
+      <c r="E5">
+        <v>138</v>
+      </c>
+      <c r="F5">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>127</v>
+      </c>
+      <c r="C6">
+        <v>127</v>
+      </c>
+      <c r="D6">
+        <v>127</v>
+      </c>
+      <c r="E6">
+        <v>127</v>
+      </c>
+      <c r="F6">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>129</v>
+      </c>
+      <c r="C7">
+        <v>129</v>
+      </c>
+      <c r="D7">
+        <v>129</v>
+      </c>
+      <c r="E7">
+        <v>129</v>
+      </c>
+      <c r="F7">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>111</v>
+      </c>
+      <c r="C8">
+        <v>111</v>
+      </c>
+      <c r="D8">
+        <v>111</v>
+      </c>
+      <c r="E8">
+        <v>111</v>
+      </c>
+      <c r="F8">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>110</v>
+      </c>
+      <c r="C9">
+        <v>110</v>
+      </c>
+      <c r="D9">
+        <v>110</v>
+      </c>
+      <c r="E9">
+        <v>110</v>
+      </c>
+      <c r="F9">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>130</v>
+      </c>
+      <c r="C10">
+        <v>130</v>
+      </c>
+      <c r="D10">
+        <v>130</v>
+      </c>
+      <c r="E10">
+        <v>130</v>
+      </c>
+      <c r="F10">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>135</v>
+      </c>
+      <c r="C11">
+        <v>135</v>
+      </c>
+      <c r="D11">
+        <v>135</v>
+      </c>
+      <c r="E11">
+        <v>135</v>
+      </c>
+      <c r="F11">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E843B933-4F2B-4E13-997D-B0F81838FA75}">
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="6">
+        <v>0</v>
+      </c>
+      <c r="C2" s="6">
+        <v>20</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6">
+        <v>15</v>
+      </c>
+      <c r="F2" s="6">
+        <v>30</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6">
+        <v>50</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0</v>
+      </c>
+      <c r="J2" s="6">
+        <v>0</v>
+      </c>
+      <c r="K2" s="6">
+        <v>0</v>
+      </c>
+      <c r="L2" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="6">
+        <v>20</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
+        <v>10</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="6">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <v>25</v>
+      </c>
+      <c r="F4" s="6">
+        <v>20</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0</v>
+      </c>
+      <c r="L4" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="6">
+        <v>15</v>
+      </c>
+      <c r="C5" s="6">
+        <v>10</v>
+      </c>
+      <c r="D5" s="6">
+        <v>25</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="6">
+        <v>30</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6">
+        <v>20</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
+        <v>25</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6">
+        <v>30</v>
+      </c>
+      <c r="J6" s="6">
+        <v>15</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0</v>
+      </c>
+      <c r="L6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>25</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>15</v>
+      </c>
+      <c r="J7" s="6">
+        <v>20</v>
+      </c>
+      <c r="K7" s="6">
+        <v>25</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="6">
+        <v>50</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6">
+        <v>20</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" s="6">
+        <v>0</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>30</v>
+      </c>
+      <c r="G9" s="6">
+        <v>15</v>
+      </c>
+      <c r="H9" s="6">
+        <v>20</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <v>15</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>15</v>
+      </c>
+      <c r="G10" s="6">
+        <v>20</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6">
+        <v>15</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6">
+        <v>15</v>
+      </c>
+      <c r="L10" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="6">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>25</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6">
+        <v>15</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="6">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6">
+        <v>15</v>
+      </c>
+      <c r="J12" s="6">
+        <v>30</v>
+      </c>
+      <c r="K12" s="6">
+        <v>25</v>
+      </c>
+      <c r="L12" s="6">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{255C87A5-1D01-4086-B297-2EB992AA260A}">
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="6">
+        <v>0</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0.51</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0.42</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0</v>
+      </c>
+      <c r="J2" s="6">
+        <v>0</v>
+      </c>
+      <c r="K2" s="6">
+        <v>0</v>
+      </c>
+      <c r="L2" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="C3" s="6">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0</v>
+      </c>
+      <c r="L3" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="6">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0</v>
+      </c>
+      <c r="L4" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="6">
+        <v>0.51</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="6">
+        <v>0.42</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.47</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0</v>
+      </c>
+      <c r="L6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="6">
+        <v>0</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.47</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0.52</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0.45</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0.52</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.32</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" s="6">
+        <v>0</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.52</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0.32</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0.48</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.45</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0.48</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0.33</v>
+      </c>
+      <c r="L10" s="6">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="6">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.52</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0.33</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="6">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0.47</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0.53</v>
+      </c>
+      <c r="L12" s="6">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
